--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-URT-FRM-11_kesinti_sonrasi_yeniden_baslatma_ve_urun_uygunlugu_dogr.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-URT-FRM-11_kesinti_sonrasi_yeniden_baslatma_ve_urun_uygunlugu_dogr.xlsx
@@ -1075,7 +1075,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-11&amp;C&amp;"Arial,Regular"&amp;11Kesinti Sonrası Yeniden Başlatma ve Ürün Uygunluğu Doğrulama Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Yeniden başlatma kontrolünde ayar/yazılım ve kalibrasyon ayrıldı; sapma izninin yasal sınırı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d0b53da4e8e463e"/>
   <x:tableParts count="1">
@@ -1401,7 +1402,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-11&amp;C&amp;"Arial,Regular"&amp;11Kesinti Sonrası Yeniden Başlatma ve Ürün Uygunluğu Doğrulama Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Yeniden başlatma kontrolünde ayar/yazılım ve kalibrasyon ayrıldı; sapma izninin yasal sınırı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a902d372da04716"/>
   <x:tableParts count="1">
@@ -1743,7 +1745,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-11&amp;C&amp;"Arial,Regular"&amp;11Kesinti Sonrası Yeniden Başlatma ve Ürün Uygunluğu Doğrulama Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Yeniden başlatma kontrolünde ayar/yazılım ve kalibrasyon ayrıldı; sapma izninin yasal sınırı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb481b15934428d"/>
   <x:tableParts count="1">
